--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2020_valparaiso.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2020_valparaiso.xlsx
@@ -168,7 +168,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 19:56</t>
+    <t xml:space="preserve">2026-08-03 09:36</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2020_valparaiso.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2020_valparaiso.xlsx
@@ -168,7 +168,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-03 09:36</t>
+    <t xml:space="preserve">2026-08-05 10:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2020_valparaiso.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2020_valparaiso.xlsx
@@ -168,7 +168,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-05 10:40</t>
+    <t xml:space="preserve">2026-08-16 09:51</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2020_valparaiso.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2020_valparaiso.xlsx
@@ -168,7 +168,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-16 09:51</t>
+    <t xml:space="preserve">2026-08-19 12:25</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2020_valparaiso.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2020_valparaiso.xlsx
@@ -168,7 +168,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-19 12:25</t>
+    <t xml:space="preserve">2026-08-28 11:34</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2020_valparaiso.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2020_valparaiso.xlsx
@@ -168,7 +168,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-28 11:34</t>
+    <t xml:space="preserve">2026-09-06 17:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
